--- a/projects/lca/04_Burden_shifting/01_Notebooks/Data/unit_conversion.xlsx
+++ b/projects/lca/04_Burden_shifting/01_Notebooks/Data/unit_conversion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\PycharmProjects\EnergyScope-Quebec\projects\lca\04_Burden_shifting\01_Notebooks\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A53CDA-6990-49CE-AF66-7B874B60ABA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B524F887-BCCE-4D2C-AC20-93E582BEC5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6225" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6225" uniqueCount="1041">
   <si>
     <t>Name</t>
   </si>
@@ -2491,9 +2491,6 @@
   </si>
   <si>
     <t>natural gas density (0.777 kg/m3): \cite{engineeringtoolbox2003}</t>
-  </si>
-  <si>
-    <t>dry wood LHV (4.28 kWh/kg): \cite{engineeringtoolbox2003}</t>
   </si>
   <si>
     <t>diesel LHV (11.83 kWh/kg): \cite{engineeringtoolbox2003}</t>
@@ -3621,7 +3618,7 @@
         <v>730</v>
       </c>
       <c r="F4" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -3659,7 +3656,7 @@
         <v>730</v>
       </c>
       <c r="F6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -3845,7 +3842,7 @@
         <v>730</v>
       </c>
       <c r="F16" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -3866,7 +3863,7 @@
         <v>723</v>
       </c>
       <c r="F17" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -3925,7 +3922,7 @@
         <v>730</v>
       </c>
       <c r="F20" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -4329,7 +4326,7 @@
         <v>730</v>
       </c>
       <c r="F40" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -4350,7 +4347,7 @@
         <v>723</v>
       </c>
       <c r="F41" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -4531,7 +4528,7 @@
         <v>730</v>
       </c>
       <c r="F50" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -4573,7 +4570,7 @@
         <v>730</v>
       </c>
       <c r="F52" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -4691,7 +4688,7 @@
         <v>730</v>
       </c>
       <c r="F58" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4733,7 +4730,7 @@
         <v>730</v>
       </c>
       <c r="F60" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -5244,7 +5241,7 @@
         <v>725</v>
       </c>
       <c r="F86" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -5286,7 +5283,7 @@
         <v>725</v>
       </c>
       <c r="F88" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -5328,7 +5325,7 @@
         <v>725</v>
       </c>
       <c r="F90" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -5370,7 +5367,7 @@
         <v>725</v>
       </c>
       <c r="F92" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -5412,7 +5409,7 @@
         <v>725</v>
       </c>
       <c r="F94" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -5454,7 +5451,7 @@
         <v>725</v>
       </c>
       <c r="F96" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -5496,7 +5493,7 @@
         <v>725</v>
       </c>
       <c r="F98" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
@@ -5538,7 +5535,7 @@
         <v>725</v>
       </c>
       <c r="F100" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
@@ -5580,7 +5577,7 @@
         <v>725</v>
       </c>
       <c r="F102" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -5622,7 +5619,7 @@
         <v>725</v>
       </c>
       <c r="F104" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -5664,7 +5661,7 @@
         <v>725</v>
       </c>
       <c r="F106" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
@@ -5706,7 +5703,7 @@
         <v>725</v>
       </c>
       <c r="F108" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -5748,7 +5745,7 @@
         <v>725</v>
       </c>
       <c r="F110" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -5790,7 +5787,7 @@
         <v>725</v>
       </c>
       <c r="F112" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -5832,7 +5829,7 @@
         <v>725</v>
       </c>
       <c r="F114" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
@@ -5874,7 +5871,7 @@
         <v>725</v>
       </c>
       <c r="F116" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
@@ -5916,7 +5913,7 @@
         <v>725</v>
       </c>
       <c r="F118" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
@@ -5958,7 +5955,7 @@
         <v>725</v>
       </c>
       <c r="F120" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
@@ -6000,7 +5997,7 @@
         <v>725</v>
       </c>
       <c r="F122" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
@@ -6042,7 +6039,7 @@
         <v>725</v>
       </c>
       <c r="F124" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -6084,7 +6081,7 @@
         <v>725</v>
       </c>
       <c r="F126" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -6126,7 +6123,7 @@
         <v>725</v>
       </c>
       <c r="F128" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -6168,7 +6165,7 @@
         <v>725</v>
       </c>
       <c r="F130" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
@@ -6210,7 +6207,7 @@
         <v>725</v>
       </c>
       <c r="F132" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
@@ -6252,7 +6249,7 @@
         <v>725</v>
       </c>
       <c r="F134" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
@@ -6294,7 +6291,7 @@
         <v>725</v>
       </c>
       <c r="F136" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
@@ -6336,7 +6333,7 @@
         <v>725</v>
       </c>
       <c r="F138" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
@@ -6378,7 +6375,7 @@
         <v>725</v>
       </c>
       <c r="F140" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
@@ -6420,7 +6417,7 @@
         <v>725</v>
       </c>
       <c r="F142" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
@@ -6462,7 +6459,7 @@
         <v>725</v>
       </c>
       <c r="F144" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
@@ -6504,7 +6501,7 @@
         <v>725</v>
       </c>
       <c r="F146" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
@@ -6546,7 +6543,7 @@
         <v>725</v>
       </c>
       <c r="F148" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
@@ -6588,7 +6585,7 @@
         <v>725</v>
       </c>
       <c r="F150" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
@@ -6630,7 +6627,7 @@
         <v>725</v>
       </c>
       <c r="F152" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
@@ -6672,7 +6669,7 @@
         <v>725</v>
       </c>
       <c r="F154" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
@@ -6714,7 +6711,7 @@
         <v>725</v>
       </c>
       <c r="F156" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
@@ -6756,7 +6753,7 @@
         <v>725</v>
       </c>
       <c r="F158" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
@@ -6798,7 +6795,7 @@
         <v>725</v>
       </c>
       <c r="F160" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
@@ -6840,7 +6837,7 @@
         <v>725</v>
       </c>
       <c r="F162" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
@@ -6882,7 +6879,7 @@
         <v>725</v>
       </c>
       <c r="F164" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
@@ -6924,7 +6921,7 @@
         <v>725</v>
       </c>
       <c r="F166" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
@@ -6966,7 +6963,7 @@
         <v>725</v>
       </c>
       <c r="F168" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
@@ -7008,7 +7005,7 @@
         <v>725</v>
       </c>
       <c r="F170" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
@@ -7050,7 +7047,7 @@
         <v>725</v>
       </c>
       <c r="F172" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
@@ -7092,7 +7089,7 @@
         <v>725</v>
       </c>
       <c r="F174" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
@@ -7134,7 +7131,7 @@
         <v>725</v>
       </c>
       <c r="F176" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
@@ -7176,7 +7173,7 @@
         <v>725</v>
       </c>
       <c r="F178" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
@@ -7218,7 +7215,7 @@
         <v>725</v>
       </c>
       <c r="F180" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
@@ -7260,7 +7257,7 @@
         <v>725</v>
       </c>
       <c r="F182" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
@@ -7302,7 +7299,7 @@
         <v>725</v>
       </c>
       <c r="F184" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
@@ -7344,7 +7341,7 @@
         <v>725</v>
       </c>
       <c r="F186" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
@@ -7386,7 +7383,7 @@
         <v>725</v>
       </c>
       <c r="F188" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
@@ -7407,7 +7404,7 @@
         <v>730</v>
       </c>
       <c r="F189" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
@@ -7446,7 +7443,7 @@
         <v>730</v>
       </c>
       <c r="F191" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
@@ -7641,7 +7638,7 @@
         <v>723</v>
       </c>
       <c r="F201" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
@@ -7683,7 +7680,7 @@
         <v>723</v>
       </c>
       <c r="F203" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
@@ -9098,7 +9095,7 @@
         <v>730</v>
       </c>
       <c r="F275" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
@@ -9137,7 +9134,7 @@
         <v>730</v>
       </c>
       <c r="F277" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
@@ -9176,7 +9173,7 @@
         <v>730</v>
       </c>
       <c r="F279" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
@@ -9214,7 +9211,7 @@
         <v>730</v>
       </c>
       <c r="F281" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
@@ -9236,7 +9233,7 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B283" t="s">
         <v>718</v>
@@ -9252,12 +9249,12 @@
         <v>732</v>
       </c>
       <c r="F283" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B284" t="s">
         <v>719</v>
@@ -9274,7 +9271,7 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B285" t="s">
         <v>718</v>
@@ -9290,12 +9287,12 @@
         <v>732</v>
       </c>
       <c r="F285" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B286" t="s">
         <v>719</v>
@@ -9328,7 +9325,7 @@
         <v>732</v>
       </c>
       <c r="F287" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.35">
@@ -9366,7 +9363,7 @@
         <v>732</v>
       </c>
       <c r="F289" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.35">
@@ -9404,7 +9401,7 @@
         <v>730</v>
       </c>
       <c r="F291" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
@@ -9425,7 +9422,7 @@
         <v>723</v>
       </c>
       <c r="F292" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
@@ -9446,7 +9443,7 @@
         <v>730</v>
       </c>
       <c r="F293" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
@@ -9488,7 +9485,7 @@
         <v>730</v>
       </c>
       <c r="F295" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
@@ -9509,7 +9506,7 @@
         <v>723</v>
       </c>
       <c r="F296" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.35">
@@ -9530,7 +9527,7 @@
         <v>731</v>
       </c>
       <c r="F297" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
@@ -9603,7 +9600,7 @@
         <v>731</v>
       </c>
       <c r="F301" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
@@ -9676,7 +9673,7 @@
         <v>730</v>
       </c>
       <c r="F305" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
@@ -9697,7 +9694,7 @@
         <v>723</v>
       </c>
       <c r="F306" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
@@ -9718,7 +9715,7 @@
         <v>730</v>
       </c>
       <c r="F307" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
@@ -9757,7 +9754,7 @@
         <v>730</v>
       </c>
       <c r="F309" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
@@ -9834,7 +9831,7 @@
         <v>730</v>
       </c>
       <c r="F313" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.35">
@@ -9873,7 +9870,7 @@
         <v>730</v>
       </c>
       <c r="F315" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
@@ -9894,7 +9891,7 @@
         <v>723</v>
       </c>
       <c r="F316" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
@@ -9966,7 +9963,7 @@
         <v>730</v>
       </c>
       <c r="F320" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
@@ -10043,7 +10040,7 @@
         <v>722</v>
       </c>
       <c r="F324" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
@@ -10064,7 +10061,7 @@
         <v>730</v>
       </c>
       <c r="F325" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
@@ -10120,7 +10117,7 @@
         <v>722</v>
       </c>
       <c r="F328" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -10141,7 +10138,7 @@
         <v>730</v>
       </c>
       <c r="F329" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
@@ -10179,7 +10176,7 @@
         <v>730</v>
       </c>
       <c r="F331" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
@@ -10239,7 +10236,7 @@
         <v>730</v>
       </c>
       <c r="F334" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
@@ -10316,7 +10313,7 @@
         <v>730</v>
       </c>
       <c r="F338" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
@@ -10471,7 +10468,7 @@
         <v>730</v>
       </c>
       <c r="F346" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
@@ -10544,7 +10541,7 @@
         <v>730</v>
       </c>
       <c r="F350" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
@@ -10565,7 +10562,7 @@
         <v>723</v>
       </c>
       <c r="F351" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
@@ -10637,7 +10634,7 @@
         <v>730</v>
       </c>
       <c r="F355" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
@@ -10697,7 +10694,7 @@
         <v>730</v>
       </c>
       <c r="F358" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
@@ -10797,7 +10794,7 @@
         <v>730</v>
       </c>
       <c r="F363" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
@@ -10818,7 +10815,7 @@
         <v>723</v>
       </c>
       <c r="F364" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
@@ -10873,7 +10870,7 @@
         <v>722</v>
       </c>
       <c r="F367" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
@@ -10894,7 +10891,7 @@
         <v>730</v>
       </c>
       <c r="F368" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
@@ -10933,7 +10930,7 @@
         <v>730</v>
       </c>
       <c r="F370" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
@@ -10972,7 +10969,7 @@
         <v>730</v>
       </c>
       <c r="F372" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
@@ -11014,7 +11011,7 @@
         <v>723</v>
       </c>
       <c r="F374" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
@@ -11069,7 +11066,7 @@
         <v>730</v>
       </c>
       <c r="F377" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -11209,7 +11206,7 @@
         <v>723</v>
       </c>
       <c r="F384" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
@@ -11293,7 +11290,7 @@
         <v>723</v>
       </c>
       <c r="F388" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
@@ -11592,7 +11589,7 @@
         <v>723</v>
       </c>
       <c r="F403" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
@@ -11613,7 +11610,7 @@
         <v>730</v>
       </c>
       <c r="F404" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
@@ -11693,7 +11690,7 @@
         <v>730</v>
       </c>
       <c r="F408" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
@@ -11794,7 +11791,7 @@
         <v>723</v>
       </c>
       <c r="F413" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
@@ -11815,7 +11812,7 @@
         <v>730</v>
       </c>
       <c r="F414" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
@@ -11853,7 +11850,7 @@
         <v>730</v>
       </c>
       <c r="F416" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.35">
@@ -11892,7 +11889,7 @@
         <v>730</v>
       </c>
       <c r="F418" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.35">
@@ -11934,7 +11931,7 @@
         <v>730</v>
       </c>
       <c r="F420" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
@@ -11976,7 +11973,7 @@
         <v>730</v>
       </c>
       <c r="F422" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.35">
@@ -12060,7 +12057,7 @@
         <v>730</v>
       </c>
       <c r="F426" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
@@ -12123,7 +12120,7 @@
         <v>730</v>
       </c>
       <c r="F429" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
@@ -12186,7 +12183,7 @@
         <v>730</v>
       </c>
       <c r="F432" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
@@ -12291,7 +12288,7 @@
         <v>730</v>
       </c>
       <c r="F437" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
@@ -12330,7 +12327,7 @@
         <v>730</v>
       </c>
       <c r="F439" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
@@ -12408,7 +12405,7 @@
         <v>730</v>
       </c>
       <c r="F443" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.35">
@@ -12429,7 +12426,7 @@
         <v>730</v>
       </c>
       <c r="F444" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.35">
@@ -12468,7 +12465,7 @@
         <v>730</v>
       </c>
       <c r="F446" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.35">
@@ -12489,7 +12486,7 @@
         <v>723</v>
       </c>
       <c r="F447" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.35">
@@ -12510,7 +12507,7 @@
         <v>730</v>
       </c>
       <c r="F448" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
@@ -12552,7 +12549,7 @@
         <v>722</v>
       </c>
       <c r="F450" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
@@ -12590,7 +12587,7 @@
         <v>730</v>
       </c>
       <c r="F452" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
@@ -12629,7 +12626,7 @@
         <v>730</v>
       </c>
       <c r="F454" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.35">
@@ -12668,7 +12665,7 @@
         <v>730</v>
       </c>
       <c r="F456" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
@@ -12707,7 +12704,7 @@
         <v>730</v>
       </c>
       <c r="F458" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.35">
@@ -12784,7 +12781,7 @@
         <v>730</v>
       </c>
       <c r="F462" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.35">
@@ -12823,7 +12820,7 @@
         <v>730</v>
       </c>
       <c r="F464" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
@@ -12862,7 +12859,7 @@
         <v>730</v>
       </c>
       <c r="F466" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.35">
@@ -12901,7 +12898,7 @@
         <v>730</v>
       </c>
       <c r="F468" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
@@ -12922,7 +12919,7 @@
         <v>723</v>
       </c>
       <c r="F469" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
@@ -12994,7 +12991,7 @@
         <v>730</v>
       </c>
       <c r="F473" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.35">
@@ -13033,7 +13030,7 @@
         <v>730</v>
       </c>
       <c r="F475" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.35">
@@ -13154,7 +13151,7 @@
         <v>730</v>
       </c>
       <c r="F481" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.35">
@@ -13175,7 +13172,7 @@
         <v>723</v>
       </c>
       <c r="F482" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.35">
@@ -13247,7 +13244,7 @@
         <v>730</v>
       </c>
       <c r="F486" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.35">
@@ -13285,7 +13282,7 @@
         <v>730</v>
       </c>
       <c r="F488" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.35">
@@ -13345,7 +13342,7 @@
         <v>733</v>
       </c>
       <c r="F491" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.35">
@@ -13383,7 +13380,7 @@
         <v>733</v>
       </c>
       <c r="F493" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.35">
@@ -13421,7 +13418,7 @@
         <v>733</v>
       </c>
       <c r="F495" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.35">
@@ -13459,7 +13456,7 @@
         <v>733</v>
       </c>
       <c r="F497" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.35">
@@ -13497,7 +13494,7 @@
         <v>733</v>
       </c>
       <c r="F499" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.35">
@@ -13535,7 +13532,7 @@
         <v>733</v>
       </c>
       <c r="F501" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.35">
@@ -13573,7 +13570,7 @@
         <v>733</v>
       </c>
       <c r="F503" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.35">
@@ -13611,7 +13608,7 @@
         <v>733</v>
       </c>
       <c r="F505" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.35">
@@ -13649,7 +13646,7 @@
         <v>733</v>
       </c>
       <c r="F507" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.35">
@@ -13687,7 +13684,7 @@
         <v>733</v>
       </c>
       <c r="F509" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.35">
@@ -13725,7 +13722,7 @@
         <v>733</v>
       </c>
       <c r="F511" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.35">
@@ -13763,7 +13760,7 @@
         <v>733</v>
       </c>
       <c r="F513" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.35">
@@ -13801,7 +13798,7 @@
         <v>733</v>
       </c>
       <c r="F515" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.35">
@@ -13839,7 +13836,7 @@
         <v>733</v>
       </c>
       <c r="F517" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.35">
@@ -13877,7 +13874,7 @@
         <v>733</v>
       </c>
       <c r="F519" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.35">
@@ -13915,7 +13912,7 @@
         <v>733</v>
       </c>
       <c r="F521" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.35">
@@ -13953,7 +13950,7 @@
         <v>733</v>
       </c>
       <c r="F523" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.35">
@@ -13991,7 +13988,7 @@
         <v>733</v>
       </c>
       <c r="F525" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.35">
@@ -14071,7 +14068,7 @@
         <v>730</v>
       </c>
       <c r="F529" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.35">
@@ -14113,7 +14110,7 @@
         <v>723</v>
       </c>
       <c r="F531" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.35">
@@ -14134,7 +14131,7 @@
         <v>730</v>
       </c>
       <c r="F532" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.35">
@@ -14197,7 +14194,7 @@
         <v>723</v>
       </c>
       <c r="F535" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.35">
@@ -14344,7 +14341,7 @@
         <v>723</v>
       </c>
       <c r="F542" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.35">
@@ -14386,7 +14383,7 @@
         <v>723</v>
       </c>
       <c r="F544" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.35">
@@ -14425,7 +14422,7 @@
         <v>730</v>
       </c>
       <c r="F546" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.35">
@@ -14446,7 +14443,7 @@
         <v>730</v>
       </c>
       <c r="F547" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.35">
@@ -14485,7 +14482,7 @@
         <v>730</v>
       </c>
       <c r="F549" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.35">
@@ -14524,7 +14521,7 @@
         <v>730</v>
       </c>
       <c r="F551" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.35">
@@ -14566,7 +14563,7 @@
         <v>730</v>
       </c>
       <c r="F553" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.35">
@@ -14608,7 +14605,7 @@
         <v>730</v>
       </c>
       <c r="F555" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.35">
@@ -14692,7 +14689,7 @@
         <v>730</v>
       </c>
       <c r="F559" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.35">
@@ -14755,7 +14752,7 @@
         <v>730</v>
       </c>
       <c r="F562" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.35">
@@ -14818,7 +14815,7 @@
         <v>730</v>
       </c>
       <c r="F565" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.35">
@@ -14923,7 +14920,7 @@
         <v>730</v>
       </c>
       <c r="F570" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.35">
@@ -14965,7 +14962,7 @@
         <v>730</v>
       </c>
       <c r="F572" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.35">
@@ -15107,7 +15104,7 @@
         <v>730</v>
       </c>
       <c r="F579" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.35">
@@ -15145,7 +15142,7 @@
         <v>730</v>
       </c>
       <c r="F581" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.35">
@@ -15166,7 +15163,7 @@
         <v>723</v>
       </c>
       <c r="F582" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.35">
@@ -15187,7 +15184,7 @@
         <v>730</v>
       </c>
       <c r="F583" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.35">
@@ -15208,7 +15205,7 @@
         <v>723</v>
       </c>
       <c r="F584" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.35">
@@ -15229,7 +15226,7 @@
         <v>730</v>
       </c>
       <c r="F585" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.35">
@@ -15400,7 +15397,7 @@
         <v>730</v>
       </c>
       <c r="F594" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.35">
@@ -15438,7 +15435,7 @@
         <v>730</v>
       </c>
       <c r="F596" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.35">
@@ -15842,7 +15839,7 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B618" t="s">
         <v>718</v>
@@ -15858,12 +15855,12 @@
         <v>730</v>
       </c>
       <c r="F618" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B619" t="s">
         <v>719</v>
@@ -15881,7 +15878,7 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B620" t="s">
         <v>718</v>
@@ -15897,12 +15894,12 @@
         <v>730</v>
       </c>
       <c r="F620" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B621" t="s">
         <v>719</v>
@@ -16012,7 +16009,7 @@
         <v>723</v>
       </c>
       <c r="F626" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.35">
@@ -16384,7 +16381,7 @@
         <v>733</v>
       </c>
       <c r="F645" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.35">
@@ -16422,7 +16419,7 @@
         <v>733</v>
       </c>
       <c r="F647" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.35">
@@ -16460,7 +16457,7 @@
         <v>733</v>
       </c>
       <c r="F649" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.35">
@@ -16498,7 +16495,7 @@
         <v>733</v>
       </c>
       <c r="F651" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.35">
@@ -16536,7 +16533,7 @@
         <v>733</v>
       </c>
       <c r="F653" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.35">
@@ -16574,7 +16571,7 @@
         <v>733</v>
       </c>
       <c r="F655" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.35">
@@ -16612,7 +16609,7 @@
         <v>733</v>
       </c>
       <c r="F657" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.35">
@@ -16650,7 +16647,7 @@
         <v>733</v>
       </c>
       <c r="F659" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.35">
@@ -16688,7 +16685,7 @@
         <v>733</v>
       </c>
       <c r="F661" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.35">
@@ -16726,7 +16723,7 @@
         <v>733</v>
       </c>
       <c r="F663" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.35">
@@ -16764,7 +16761,7 @@
         <v>733</v>
       </c>
       <c r="F665" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.35">
@@ -16802,7 +16799,7 @@
         <v>733</v>
       </c>
       <c r="F667" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.35">
@@ -16840,7 +16837,7 @@
         <v>733</v>
       </c>
       <c r="F669" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.35">
@@ -16878,7 +16875,7 @@
         <v>733</v>
       </c>
       <c r="F671" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.35">
@@ -16916,7 +16913,7 @@
         <v>733</v>
       </c>
       <c r="F673" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.35">
@@ -16954,7 +16951,7 @@
         <v>733</v>
       </c>
       <c r="F675" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.35">
@@ -16992,7 +16989,7 @@
         <v>733</v>
       </c>
       <c r="F677" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.35">
@@ -17030,7 +17027,7 @@
         <v>733</v>
       </c>
       <c r="F679" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.35">
@@ -17068,7 +17065,7 @@
         <v>733</v>
       </c>
       <c r="F681" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.35">
@@ -17106,7 +17103,7 @@
         <v>733</v>
       </c>
       <c r="F683" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.35">
@@ -17144,7 +17141,7 @@
         <v>733</v>
       </c>
       <c r="F685" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.35">
@@ -17182,7 +17179,7 @@
         <v>733</v>
       </c>
       <c r="F687" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.35">
@@ -17220,7 +17217,7 @@
         <v>733</v>
       </c>
       <c r="F689" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.35">
@@ -17258,7 +17255,7 @@
         <v>733</v>
       </c>
       <c r="F691" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.35">
@@ -17536,7 +17533,7 @@
         <v>730</v>
       </c>
       <c r="F705" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.35">
@@ -17872,7 +17869,7 @@
         <v>725</v>
       </c>
       <c r="F723" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.35">
@@ -17914,7 +17911,7 @@
         <v>725</v>
       </c>
       <c r="F725" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.35">
@@ -17956,7 +17953,7 @@
         <v>725</v>
       </c>
       <c r="F727" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.35">
@@ -17998,7 +17995,7 @@
         <v>725</v>
       </c>
       <c r="F729" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.35">
@@ -18040,7 +18037,7 @@
         <v>725</v>
       </c>
       <c r="F731" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.35">
@@ -18082,7 +18079,7 @@
         <v>725</v>
       </c>
       <c r="F733" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.35">
@@ -18124,7 +18121,7 @@
         <v>725</v>
       </c>
       <c r="F735" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.35">
@@ -18166,7 +18163,7 @@
         <v>725</v>
       </c>
       <c r="F737" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.35">
@@ -18208,7 +18205,7 @@
         <v>725</v>
       </c>
       <c r="F739" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.35">
@@ -18250,7 +18247,7 @@
         <v>725</v>
       </c>
       <c r="F741" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.35">
@@ -18292,7 +18289,7 @@
         <v>725</v>
       </c>
       <c r="F743" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.35">
@@ -18334,7 +18331,7 @@
         <v>725</v>
       </c>
       <c r="F745" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.35">
@@ -18376,7 +18373,7 @@
         <v>725</v>
       </c>
       <c r="F747" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.35">
@@ -18418,7 +18415,7 @@
         <v>725</v>
       </c>
       <c r="F749" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.35">
@@ -18460,7 +18457,7 @@
         <v>725</v>
       </c>
       <c r="F751" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.35">
@@ -18502,7 +18499,7 @@
         <v>725</v>
       </c>
       <c r="F753" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.35">
@@ -18544,7 +18541,7 @@
         <v>725</v>
       </c>
       <c r="F755" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.35">
@@ -18586,7 +18583,7 @@
         <v>725</v>
       </c>
       <c r="F757" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.35">
@@ -18628,7 +18625,7 @@
         <v>725</v>
       </c>
       <c r="F759" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.35">
@@ -18670,7 +18667,7 @@
         <v>725</v>
       </c>
       <c r="F761" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.35">
@@ -18712,7 +18709,7 @@
         <v>725</v>
       </c>
       <c r="F763" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.35">
@@ -18754,7 +18751,7 @@
         <v>725</v>
       </c>
       <c r="F765" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.35">
@@ -18796,7 +18793,7 @@
         <v>725</v>
       </c>
       <c r="F767" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.35">
@@ -18838,7 +18835,7 @@
         <v>725</v>
       </c>
       <c r="F769" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.35">
@@ -18880,7 +18877,7 @@
         <v>725</v>
       </c>
       <c r="F771" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.35">
@@ -18922,7 +18919,7 @@
         <v>725</v>
       </c>
       <c r="F773" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.35">
@@ -18964,7 +18961,7 @@
         <v>725</v>
       </c>
       <c r="F775" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.35">
@@ -19006,7 +19003,7 @@
         <v>725</v>
       </c>
       <c r="F777" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.35">
@@ -19048,7 +19045,7 @@
         <v>725</v>
       </c>
       <c r="F779" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.35">
@@ -19090,7 +19087,7 @@
         <v>725</v>
       </c>
       <c r="F781" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.35">
@@ -19132,7 +19129,7 @@
         <v>725</v>
       </c>
       <c r="F783" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.35">
@@ -19174,7 +19171,7 @@
         <v>725</v>
       </c>
       <c r="F785" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.35">
@@ -19216,7 +19213,7 @@
         <v>725</v>
       </c>
       <c r="F787" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.35">
@@ -19258,7 +19255,7 @@
         <v>725</v>
       </c>
       <c r="F789" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.35">
@@ -19300,7 +19297,7 @@
         <v>725</v>
       </c>
       <c r="F791" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.35">
@@ -19342,7 +19339,7 @@
         <v>725</v>
       </c>
       <c r="F793" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.35">
@@ -19384,7 +19381,7 @@
         <v>725</v>
       </c>
       <c r="F795" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.35">
@@ -19426,7 +19423,7 @@
         <v>725</v>
       </c>
       <c r="F797" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.35">
@@ -19468,7 +19465,7 @@
         <v>725</v>
       </c>
       <c r="F799" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.35">
@@ -19510,7 +19507,7 @@
         <v>725</v>
       </c>
       <c r="F801" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.35">
@@ -19552,7 +19549,7 @@
         <v>725</v>
       </c>
       <c r="F803" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.35">
@@ -19594,7 +19591,7 @@
         <v>725</v>
       </c>
       <c r="F805" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.35">
@@ -19636,7 +19633,7 @@
         <v>725</v>
       </c>
       <c r="F807" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.35">
@@ -19678,7 +19675,7 @@
         <v>725</v>
       </c>
       <c r="F809" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.35">
@@ -19720,7 +19717,7 @@
         <v>725</v>
       </c>
       <c r="F811" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.35">
@@ -19762,7 +19759,7 @@
         <v>725</v>
       </c>
       <c r="F813" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.35">
@@ -19804,7 +19801,7 @@
         <v>725</v>
       </c>
       <c r="F815" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.35">
@@ -19846,7 +19843,7 @@
         <v>725</v>
       </c>
       <c r="F817" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.35">
@@ -20185,7 +20182,7 @@
         <v>733</v>
       </c>
       <c r="F835" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.35">
@@ -20222,7 +20219,7 @@
         <v>722</v>
       </c>
       <c r="F837" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.35">
@@ -20242,7 +20239,7 @@
         <v>722</v>
       </c>
       <c r="F838" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.35">
@@ -20263,7 +20260,7 @@
         <v>733</v>
       </c>
       <c r="F839" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.35">
@@ -20300,7 +20297,7 @@
         <v>722</v>
       </c>
       <c r="F841" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.35">
@@ -20320,7 +20317,7 @@
         <v>722</v>
       </c>
       <c r="F842" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.35">
@@ -20341,7 +20338,7 @@
         <v>733</v>
       </c>
       <c r="F843" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.35">
@@ -20378,7 +20375,7 @@
         <v>722</v>
       </c>
       <c r="F845" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.35">
@@ -20398,7 +20395,7 @@
         <v>722</v>
       </c>
       <c r="F846" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.35">
@@ -20419,7 +20416,7 @@
         <v>733</v>
       </c>
       <c r="F847" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.35">
@@ -20456,7 +20453,7 @@
         <v>722</v>
       </c>
       <c r="F849" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="850" spans="1:6" x14ac:dyDescent="0.35">
@@ -20476,7 +20473,7 @@
         <v>722</v>
       </c>
       <c r="F850" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.35">
@@ -20497,7 +20494,7 @@
         <v>733</v>
       </c>
       <c r="F851" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.35">
@@ -20534,7 +20531,7 @@
         <v>722</v>
       </c>
       <c r="F853" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.35">
@@ -20554,7 +20551,7 @@
         <v>722</v>
       </c>
       <c r="F854" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.35">
@@ -20575,7 +20572,7 @@
         <v>733</v>
       </c>
       <c r="F855" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.35">
@@ -20613,7 +20610,7 @@
         <v>722</v>
       </c>
       <c r="F857" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.35">
@@ -20633,7 +20630,7 @@
         <v>722</v>
       </c>
       <c r="F858" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.35">
@@ -20654,7 +20651,7 @@
         <v>733</v>
       </c>
       <c r="F859" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.35">
@@ -20692,7 +20689,7 @@
         <v>722</v>
       </c>
       <c r="F861" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.35">
@@ -20712,7 +20709,7 @@
         <v>722</v>
       </c>
       <c r="F862" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.35">
@@ -20733,7 +20730,7 @@
         <v>733</v>
       </c>
       <c r="F863" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.35">
@@ -20770,7 +20767,7 @@
         <v>722</v>
       </c>
       <c r="F865" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.35">
@@ -20790,7 +20787,7 @@
         <v>722</v>
       </c>
       <c r="F866" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="867" spans="1:6" x14ac:dyDescent="0.35">
@@ -20811,7 +20808,7 @@
         <v>733</v>
       </c>
       <c r="F867" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="868" spans="1:6" x14ac:dyDescent="0.35">
@@ -20848,7 +20845,7 @@
         <v>722</v>
       </c>
       <c r="F869" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="870" spans="1:6" x14ac:dyDescent="0.35">
@@ -20868,7 +20865,7 @@
         <v>722</v>
       </c>
       <c r="F870" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="871" spans="1:6" x14ac:dyDescent="0.35">
@@ -20889,7 +20886,7 @@
         <v>733</v>
       </c>
       <c r="F871" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="872" spans="1:6" x14ac:dyDescent="0.35">
@@ -20926,7 +20923,7 @@
         <v>722</v>
       </c>
       <c r="F873" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.35">
@@ -20946,7 +20943,7 @@
         <v>722</v>
       </c>
       <c r="F874" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.35">
@@ -21123,7 +21120,7 @@
         <v>732</v>
       </c>
       <c r="F883" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="884" spans="1:6" x14ac:dyDescent="0.35">
@@ -21162,7 +21159,7 @@
         <v>733</v>
       </c>
       <c r="F885" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="886" spans="1:6" x14ac:dyDescent="0.35">
@@ -21200,7 +21197,7 @@
         <v>733</v>
       </c>
       <c r="F887" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.35">
@@ -21238,7 +21235,7 @@
         <v>733</v>
       </c>
       <c r="F889" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="890" spans="1:6" x14ac:dyDescent="0.35">
@@ -21276,7 +21273,7 @@
         <v>733</v>
       </c>
       <c r="F891" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="892" spans="1:6" x14ac:dyDescent="0.35">
@@ -21314,7 +21311,7 @@
         <v>733</v>
       </c>
       <c r="F893" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="894" spans="1:6" x14ac:dyDescent="0.35">
@@ -21352,7 +21349,7 @@
         <v>733</v>
       </c>
       <c r="F895" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="896" spans="1:6" x14ac:dyDescent="0.35">
@@ -21390,7 +21387,7 @@
         <v>733</v>
       </c>
       <c r="F897" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.35">
@@ -21428,7 +21425,7 @@
         <v>733</v>
       </c>
       <c r="F899" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="900" spans="1:6" x14ac:dyDescent="0.35">
@@ -21466,7 +21463,7 @@
         <v>733</v>
       </c>
       <c r="F901" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="902" spans="1:6" x14ac:dyDescent="0.35">
@@ -21504,7 +21501,7 @@
         <v>733</v>
       </c>
       <c r="F903" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="904" spans="1:6" x14ac:dyDescent="0.35">
@@ -21542,7 +21539,7 @@
         <v>733</v>
       </c>
       <c r="F905" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="906" spans="1:6" x14ac:dyDescent="0.35">
@@ -21580,7 +21577,7 @@
         <v>733</v>
       </c>
       <c r="F907" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="908" spans="1:6" x14ac:dyDescent="0.35">
@@ -21618,7 +21615,7 @@
         <v>733</v>
       </c>
       <c r="F909" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.35">
@@ -21656,7 +21653,7 @@
         <v>733</v>
       </c>
       <c r="F911" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="912" spans="1:6" x14ac:dyDescent="0.35">
@@ -21694,7 +21691,7 @@
         <v>733</v>
       </c>
       <c r="F913" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.35">
@@ -21732,7 +21729,7 @@
         <v>733</v>
       </c>
       <c r="F915" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="916" spans="1:6" x14ac:dyDescent="0.35">
@@ -21770,7 +21767,7 @@
         <v>733</v>
       </c>
       <c r="F917" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="918" spans="1:6" x14ac:dyDescent="0.35">
@@ -21808,7 +21805,7 @@
         <v>733</v>
       </c>
       <c r="F919" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="920" spans="1:6" x14ac:dyDescent="0.35">
@@ -21846,7 +21843,7 @@
         <v>733</v>
       </c>
       <c r="F921" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="922" spans="1:6" x14ac:dyDescent="0.35">
@@ -21884,7 +21881,7 @@
         <v>733</v>
       </c>
       <c r="F923" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="924" spans="1:6" x14ac:dyDescent="0.35">
@@ -21922,7 +21919,7 @@
         <v>733</v>
       </c>
       <c r="F925" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="926" spans="1:6" x14ac:dyDescent="0.35">
@@ -21960,7 +21957,7 @@
         <v>733</v>
       </c>
       <c r="F927" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="928" spans="1:6" x14ac:dyDescent="0.35">
@@ -21998,7 +21995,7 @@
         <v>733</v>
       </c>
       <c r="F929" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="930" spans="1:6" x14ac:dyDescent="0.35">
@@ -22036,7 +22033,7 @@
         <v>733</v>
       </c>
       <c r="F931" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="932" spans="1:6" x14ac:dyDescent="0.35">
@@ -22176,7 +22173,7 @@
         <v>723</v>
       </c>
       <c r="F938" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.35">
@@ -22197,7 +22194,7 @@
         <v>730</v>
       </c>
       <c r="F939" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="940" spans="1:6" x14ac:dyDescent="0.35">
@@ -22270,7 +22267,7 @@
         <v>730</v>
       </c>
       <c r="F943" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.35">
@@ -22327,7 +22324,7 @@
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A947" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B947" t="s">
         <v>718</v>
@@ -22343,12 +22340,12 @@
         <v>730</v>
       </c>
       <c r="F947" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A948" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B948" t="s">
         <v>719</v>
@@ -22366,7 +22363,7 @@
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A949" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B949" t="s">
         <v>718</v>
@@ -22383,7 +22380,7 @@
     </row>
     <row r="950" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A950" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B950" t="s">
         <v>718</v>
@@ -22484,7 +22481,7 @@
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A955" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B955" t="s">
         <v>720</v>
@@ -22547,7 +22544,7 @@
     </row>
     <row r="958" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A958" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B958" t="s">
         <v>720</v>
@@ -22584,12 +22581,12 @@
         <v>723</v>
       </c>
       <c r="F959" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A960" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B960" t="s">
         <v>720</v>
@@ -22605,12 +22602,12 @@
         <v>723</v>
       </c>
       <c r="F960" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="961" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A961" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B961" t="s">
         <v>720</v>
@@ -22626,7 +22623,7 @@
         <v>723</v>
       </c>
       <c r="F961" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="962" spans="1:6" x14ac:dyDescent="0.35">
@@ -22647,7 +22644,7 @@
         <v>723</v>
       </c>
       <c r="F962" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="963" spans="1:6" x14ac:dyDescent="0.35">
@@ -22688,7 +22685,7 @@
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A965" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B965" t="s">
         <v>720</v>
@@ -22709,7 +22706,7 @@
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A966" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B966" t="s">
         <v>720</v>
@@ -22746,7 +22743,7 @@
         <v>723</v>
       </c>
       <c r="F967" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.35">
@@ -22803,7 +22800,7 @@
         <v>723</v>
       </c>
       <c r="F970" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="971" spans="1:6" x14ac:dyDescent="0.35">
@@ -22845,7 +22842,7 @@
         <v>723</v>
       </c>
       <c r="F972" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="973" spans="1:6" x14ac:dyDescent="0.35">
@@ -22866,7 +22863,7 @@
         <v>723</v>
       </c>
       <c r="F973" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="974" spans="1:6" x14ac:dyDescent="0.35">
@@ -22887,12 +22884,12 @@
         <v>723</v>
       </c>
       <c r="F974" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="975" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A975" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B975" t="s">
         <v>720</v>
@@ -22908,7 +22905,7 @@
         <v>723</v>
       </c>
       <c r="F975" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="976" spans="1:6" x14ac:dyDescent="0.35">
@@ -22929,12 +22926,12 @@
         <v>723</v>
       </c>
       <c r="F976" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="977" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A977" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B977" t="s">
         <v>720</v>
@@ -22992,7 +22989,7 @@
         <v>723</v>
       </c>
       <c r="F979" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="980" spans="1:6" x14ac:dyDescent="0.35">
@@ -23076,12 +23073,12 @@
         <v>723</v>
       </c>
       <c r="F983" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A984" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B984" t="s">
         <v>720</v>
@@ -23118,7 +23115,7 @@
         <v>721</v>
       </c>
       <c r="F985" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="986" spans="1:6" x14ac:dyDescent="0.35">
@@ -23139,7 +23136,7 @@
         <v>724</v>
       </c>
       <c r="F986" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="987" spans="1:6" x14ac:dyDescent="0.35">
@@ -23165,7 +23162,7 @@
     </row>
     <row r="988" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A988" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B988" t="s">
         <v>720</v>
@@ -23181,7 +23178,7 @@
         <v>723</v>
       </c>
       <c r="F988" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="989" spans="1:6" x14ac:dyDescent="0.35">
@@ -23192,8 +23189,8 @@
         <v>720</v>
       </c>
       <c r="C989">
-        <f>1/4.28</f>
-        <v>0.23364485981308411</v>
+        <f>3.6/19</f>
+        <v>0.18947368421052632</v>
       </c>
       <c r="D989" t="s">
         <v>721</v>
@@ -23202,7 +23199,7 @@
         <v>723</v>
       </c>
       <c r="F989" t="s">
-        <v>818</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="990" spans="1:6" x14ac:dyDescent="0.35">
@@ -23213,8 +23210,8 @@
         <v>720</v>
       </c>
       <c r="C990">
-        <f>1/4.28</f>
-        <v>0.23364485981308411</v>
+        <f>3.6/19</f>
+        <v>0.18947368421052632</v>
       </c>
       <c r="D990" t="s">
         <v>721</v>
@@ -23223,7 +23220,7 @@
         <v>723</v>
       </c>
       <c r="F990" t="s">
-        <v>818</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="991" spans="1:6" x14ac:dyDescent="0.35">
@@ -23234,8 +23231,8 @@
         <v>720</v>
       </c>
       <c r="C991">
-        <f>1/4.28</f>
-        <v>0.23364485981308411</v>
+        <f>3.6/19</f>
+        <v>0.18947368421052632</v>
       </c>
       <c r="D991" t="s">
         <v>721</v>
@@ -23244,7 +23241,7 @@
         <v>723</v>
       </c>
       <c r="F991" t="s">
-        <v>818</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="992" spans="1:6" x14ac:dyDescent="0.35">
@@ -23364,7 +23361,7 @@
         <v>725</v>
       </c>
       <c r="F997" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="998" spans="1:6" x14ac:dyDescent="0.35">
@@ -23406,7 +23403,7 @@
         <v>725</v>
       </c>
       <c r="F999" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1000" spans="1:6" x14ac:dyDescent="0.35">
@@ -23448,7 +23445,7 @@
         <v>725</v>
       </c>
       <c r="F1001" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1002" spans="1:6" x14ac:dyDescent="0.35">
@@ -23490,7 +23487,7 @@
         <v>725</v>
       </c>
       <c r="F1003" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1004" spans="1:6" x14ac:dyDescent="0.35">
@@ -23532,7 +23529,7 @@
         <v>725</v>
       </c>
       <c r="F1005" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1006" spans="1:6" x14ac:dyDescent="0.35">
@@ -23574,7 +23571,7 @@
         <v>725</v>
       </c>
       <c r="F1007" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1008" spans="1:6" x14ac:dyDescent="0.35">
@@ -23616,7 +23613,7 @@
         <v>725</v>
       </c>
       <c r="F1009" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1010" spans="1:6" x14ac:dyDescent="0.35">
@@ -23658,7 +23655,7 @@
         <v>725</v>
       </c>
       <c r="F1011" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1012" spans="1:6" x14ac:dyDescent="0.35">
@@ -23700,7 +23697,7 @@
         <v>725</v>
       </c>
       <c r="F1013" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1014" spans="1:6" x14ac:dyDescent="0.35">
@@ -23742,7 +23739,7 @@
         <v>725</v>
       </c>
       <c r="F1015" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1016" spans="1:6" x14ac:dyDescent="0.35">
@@ -23784,7 +23781,7 @@
         <v>725</v>
       </c>
       <c r="F1017" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1018" spans="1:6" x14ac:dyDescent="0.35">
@@ -23826,7 +23823,7 @@
         <v>725</v>
       </c>
       <c r="F1019" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1020" spans="1:6" x14ac:dyDescent="0.35">
@@ -23868,7 +23865,7 @@
         <v>725</v>
       </c>
       <c r="F1021" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1022" spans="1:6" x14ac:dyDescent="0.35">
@@ -23910,7 +23907,7 @@
         <v>725</v>
       </c>
       <c r="F1023" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1024" spans="1:6" x14ac:dyDescent="0.35">
@@ -23952,7 +23949,7 @@
         <v>725</v>
       </c>
       <c r="F1025" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1026" spans="1:6" x14ac:dyDescent="0.35">
@@ -23994,7 +23991,7 @@
         <v>725</v>
       </c>
       <c r="F1027" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1028" spans="1:6" x14ac:dyDescent="0.35">
@@ -24015,7 +24012,7 @@
         <v>730</v>
       </c>
       <c r="F1028" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="1029" spans="1:6" x14ac:dyDescent="0.35">
@@ -24054,7 +24051,7 @@
         <v>730</v>
       </c>
       <c r="F1030" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="1031" spans="1:6" x14ac:dyDescent="0.35">
@@ -24327,7 +24324,7 @@
         <v>730</v>
       </c>
       <c r="F1044" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="1045" spans="1:6" x14ac:dyDescent="0.35">
@@ -24366,7 +24363,7 @@
         <v>730</v>
       </c>
       <c r="F1046" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="1047" spans="1:6" x14ac:dyDescent="0.35">
@@ -24443,7 +24440,7 @@
         <v>730</v>
       </c>
       <c r="F1050" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="1051" spans="1:6" x14ac:dyDescent="0.35">
@@ -24464,7 +24461,7 @@
         <v>723</v>
       </c>
       <c r="F1051" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1052" spans="1:6" x14ac:dyDescent="0.35">
@@ -24536,7 +24533,7 @@
         <v>730</v>
       </c>
       <c r="F1055" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="1056" spans="1:6" x14ac:dyDescent="0.35">
@@ -24613,7 +24610,7 @@
         <v>722</v>
       </c>
       <c r="F1059" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="1060" spans="1:6" x14ac:dyDescent="0.35">
@@ -24634,7 +24631,7 @@
         <v>730</v>
       </c>
       <c r="F1060" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="1061" spans="1:6" x14ac:dyDescent="0.35">
@@ -24827,7 +24824,7 @@
         <v>730</v>
       </c>
       <c r="F1070" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="1071" spans="1:6" x14ac:dyDescent="0.35">
@@ -24848,7 +24845,7 @@
         <v>723</v>
       </c>
       <c r="F1071" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="1072" spans="1:6" x14ac:dyDescent="0.35">
@@ -24962,7 +24959,7 @@
         <v>730</v>
       </c>
       <c r="F1077" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="1078" spans="1:6" x14ac:dyDescent="0.35">
@@ -25001,7 +24998,7 @@
         <v>730</v>
       </c>
       <c r="F1079" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="1080" spans="1:6" x14ac:dyDescent="0.35">
@@ -25040,7 +25037,7 @@
         <v>730</v>
       </c>
       <c r="F1081" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="1082" spans="1:6" x14ac:dyDescent="0.35">
@@ -25079,7 +25076,7 @@
         <v>730</v>
       </c>
       <c r="F1083" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="1084" spans="1:6" x14ac:dyDescent="0.35">
@@ -25156,7 +25153,7 @@
         <v>730</v>
       </c>
       <c r="F1087" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="1088" spans="1:6" x14ac:dyDescent="0.35">
@@ -25177,7 +25174,7 @@
         <v>723</v>
       </c>
       <c r="F1088" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="1089" spans="1:6" x14ac:dyDescent="0.35">
@@ -25249,7 +25246,7 @@
         <v>733</v>
       </c>
       <c r="F1092" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="1093" spans="1:6" x14ac:dyDescent="0.35">
@@ -25287,7 +25284,7 @@
         <v>733</v>
       </c>
       <c r="F1094" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="1095" spans="1:6" x14ac:dyDescent="0.35">
@@ -25472,7 +25469,7 @@
         <v>723</v>
       </c>
       <c r="F1103" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="1104" spans="1:6" x14ac:dyDescent="0.35">
@@ -25514,7 +25511,7 @@
         <v>723</v>
       </c>
       <c r="F1105" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="1106" spans="1:6" x14ac:dyDescent="0.35">
@@ -25535,7 +25532,7 @@
         <v>730</v>
       </c>
       <c r="F1106" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="1107" spans="1:6" x14ac:dyDescent="0.35">
@@ -25577,7 +25574,7 @@
         <v>730</v>
       </c>
       <c r="F1108" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="1109" spans="1:6" x14ac:dyDescent="0.35">
@@ -25619,7 +25616,7 @@
         <v>730</v>
       </c>
       <c r="F1110" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="1111" spans="1:6" x14ac:dyDescent="0.35">
@@ -25682,7 +25679,7 @@
         <v>730</v>
       </c>
       <c r="F1113" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="1114" spans="1:6" x14ac:dyDescent="0.35">
@@ -25745,7 +25742,7 @@
         <v>730</v>
       </c>
       <c r="F1116" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="1117" spans="1:6" x14ac:dyDescent="0.35">
@@ -25808,7 +25805,7 @@
         <v>730</v>
       </c>
       <c r="F1119" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="1120" spans="1:6" x14ac:dyDescent="0.35">
@@ -25850,7 +25847,7 @@
         <v>730</v>
       </c>
       <c r="F1121" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="1122" spans="1:6" x14ac:dyDescent="0.35">
@@ -25892,7 +25889,7 @@
         <v>730</v>
       </c>
       <c r="F1123" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="1124" spans="1:6" x14ac:dyDescent="0.35">
@@ -26014,7 +26011,7 @@
         <v>723</v>
       </c>
       <c r="F1129" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="1130" spans="1:6" x14ac:dyDescent="0.35">
@@ -26035,7 +26032,7 @@
         <v>730</v>
       </c>
       <c r="F1130" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="1131" spans="1:6" x14ac:dyDescent="0.35">
@@ -26056,7 +26053,7 @@
         <v>723</v>
       </c>
       <c r="F1131" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="1132" spans="1:6" x14ac:dyDescent="0.35">
@@ -26077,7 +26074,7 @@
         <v>730</v>
       </c>
       <c r="F1132" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="1133" spans="1:6" x14ac:dyDescent="0.35">
@@ -26098,7 +26095,7 @@
         <v>723</v>
       </c>
       <c r="F1133" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="1134" spans="1:6" x14ac:dyDescent="0.35">
@@ -26275,7 +26272,7 @@
         <v>733</v>
       </c>
       <c r="F1142" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.35">
@@ -26313,7 +26310,7 @@
         <v>733</v>
       </c>
       <c r="F1144" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="1145" spans="1:6" x14ac:dyDescent="0.35">
@@ -26351,7 +26348,7 @@
         <v>733</v>
       </c>
       <c r="F1146" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="1147" spans="1:6" x14ac:dyDescent="0.35">
@@ -26410,7 +26407,7 @@
         <v>725</v>
       </c>
       <c r="F1149" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1150" spans="1:6" x14ac:dyDescent="0.35">
@@ -26452,7 +26449,7 @@
         <v>725</v>
       </c>
       <c r="F1151" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1152" spans="1:6" x14ac:dyDescent="0.35">
@@ -26494,7 +26491,7 @@
         <v>725</v>
       </c>
       <c r="F1153" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1154" spans="1:6" x14ac:dyDescent="0.35">
@@ -26536,7 +26533,7 @@
         <v>725</v>
       </c>
       <c r="F1155" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1156" spans="1:6" x14ac:dyDescent="0.35">
@@ -26578,7 +26575,7 @@
         <v>725</v>
       </c>
       <c r="F1157" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1158" spans="1:6" x14ac:dyDescent="0.35">
@@ -26620,7 +26617,7 @@
         <v>725</v>
       </c>
       <c r="F1159" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1160" spans="1:6" x14ac:dyDescent="0.35">
@@ -26662,7 +26659,7 @@
         <v>725</v>
       </c>
       <c r="F1161" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1162" spans="1:6" x14ac:dyDescent="0.35">
@@ -26704,7 +26701,7 @@
         <v>725</v>
       </c>
       <c r="F1163" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1164" spans="1:6" x14ac:dyDescent="0.35">
@@ -26746,7 +26743,7 @@
         <v>725</v>
       </c>
       <c r="F1165" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1166" spans="1:6" x14ac:dyDescent="0.35">
@@ -26788,7 +26785,7 @@
         <v>725</v>
       </c>
       <c r="F1167" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1168" spans="1:6" x14ac:dyDescent="0.35">
@@ -26830,7 +26827,7 @@
         <v>725</v>
       </c>
       <c r="F1169" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1170" spans="1:6" x14ac:dyDescent="0.35">
@@ -26872,7 +26869,7 @@
         <v>725</v>
       </c>
       <c r="F1171" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="1172" spans="1:6" x14ac:dyDescent="0.35">
@@ -26971,7 +26968,7 @@
         <v>733</v>
       </c>
       <c r="F1176" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="1177" spans="1:6" x14ac:dyDescent="0.35">
@@ -27008,7 +27005,7 @@
         <v>722</v>
       </c>
       <c r="F1178" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="1179" spans="1:6" x14ac:dyDescent="0.35">
@@ -27028,7 +27025,7 @@
         <v>722</v>
       </c>
       <c r="F1179" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="1180" spans="1:6" x14ac:dyDescent="0.35">
@@ -27049,7 +27046,7 @@
         <v>733</v>
       </c>
       <c r="F1180" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="1181" spans="1:6" x14ac:dyDescent="0.35">
@@ -27086,7 +27083,7 @@
         <v>722</v>
       </c>
       <c r="F1182" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="1183" spans="1:6" x14ac:dyDescent="0.35">
@@ -27106,7 +27103,7 @@
         <v>722</v>
       </c>
       <c r="F1183" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="1184" spans="1:6" x14ac:dyDescent="0.35">
@@ -27127,7 +27124,7 @@
         <v>733</v>
       </c>
       <c r="F1184" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="1185" spans="1:6" x14ac:dyDescent="0.35">
@@ -27164,7 +27161,7 @@
         <v>722</v>
       </c>
       <c r="F1186" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="1187" spans="1:6" x14ac:dyDescent="0.35">
@@ -27184,7 +27181,7 @@
         <v>722</v>
       </c>
       <c r="F1187" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="1188" spans="1:6" x14ac:dyDescent="0.35">
@@ -27205,7 +27202,7 @@
         <v>733</v>
       </c>
       <c r="F1188" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="1189" spans="1:6" x14ac:dyDescent="0.35">
@@ -27242,7 +27239,7 @@
         <v>722</v>
       </c>
       <c r="F1190" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="1191" spans="1:6" x14ac:dyDescent="0.35">
@@ -27262,7 +27259,7 @@
         <v>722</v>
       </c>
       <c r="F1191" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="1192" spans="1:6" x14ac:dyDescent="0.35">
@@ -27361,7 +27358,7 @@
         <v>733</v>
       </c>
       <c r="F1196" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="1197" spans="1:6" x14ac:dyDescent="0.35">
@@ -27399,7 +27396,7 @@
         <v>733</v>
       </c>
       <c r="F1198" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="1199" spans="1:6" x14ac:dyDescent="0.35">
@@ -27437,7 +27434,7 @@
         <v>733</v>
       </c>
       <c r="F1200" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="1201" spans="1:6" x14ac:dyDescent="0.35">
@@ -27480,7 +27477,7 @@
     </row>
     <row r="1203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1203" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B1203" t="s">
         <v>718</v>
@@ -27496,12 +27493,12 @@
         <v>730</v>
       </c>
       <c r="F1203" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="1204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1204" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B1204" t="s">
         <v>718</v>
@@ -27517,12 +27514,12 @@
         <v>730</v>
       </c>
       <c r="F1204" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="1205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1205" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B1205" t="s">
         <v>718</v>
@@ -27538,12 +27535,12 @@
         <v>730</v>
       </c>
       <c r="F1205" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="1206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1206" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B1206" t="s">
         <v>718</v>
@@ -27559,12 +27556,12 @@
         <v>730</v>
       </c>
       <c r="F1206" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="1207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1207" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B1207" t="s">
         <v>718</v>
@@ -27580,12 +27577,12 @@
         <v>730</v>
       </c>
       <c r="F1207" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="1208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1208" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B1208" t="s">
         <v>718</v>
@@ -27601,12 +27598,12 @@
         <v>730</v>
       </c>
       <c r="F1208" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="1209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1209" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B1209" t="s">
         <v>718</v>
@@ -27622,12 +27619,12 @@
         <v>730</v>
       </c>
       <c r="F1209" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="1210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1210" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B1210" t="s">
         <v>718</v>
@@ -27643,7 +27640,7 @@
         <v>730</v>
       </c>
       <c r="F1210" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="1211" spans="1:6" x14ac:dyDescent="0.35">
@@ -27651,7 +27648,7 @@
         <v>6</v>
       </c>
       <c r="B1211" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1211">
         <f>1 * 3.6 / 14.55</f>
@@ -27672,7 +27669,7 @@
         <v>7</v>
       </c>
       <c r="B1212" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1212">
         <f>1 / 8.22</f>
@@ -27693,7 +27690,7 @@
         <v>27</v>
       </c>
       <c r="B1213" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1213">
         <f>1 * 3.6 / 42.5</f>
@@ -27714,7 +27711,7 @@
         <v>53</v>
       </c>
       <c r="B1214" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1214">
         <f>1 / 10.5</f>
@@ -27735,7 +27732,7 @@
         <v>150</v>
       </c>
       <c r="B1215" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1215">
         <f>1 * 3.6 / 27.91</f>
@@ -27756,7 +27753,7 @@
         <v>227</v>
       </c>
       <c r="B1216" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1216">
         <f>1 / 11.83</f>
@@ -27777,7 +27774,7 @@
         <v>232</v>
       </c>
       <c r="B1217" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1217">
         <f>1</f>
@@ -27792,10 +27789,10 @@
     </row>
     <row r="1218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1218" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B1218" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1218">
         <f>1</f>
@@ -27810,10 +27807,10 @@
     </row>
     <row r="1219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1219" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B1219" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1219">
         <f>1</f>
@@ -27828,10 +27825,10 @@
     </row>
     <row r="1220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1220" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B1220" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1220">
         <f>1</f>
@@ -27849,7 +27846,7 @@
         <v>236</v>
       </c>
       <c r="B1221" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1221">
         <f>1 / 13.28</f>
@@ -27870,7 +27867,7 @@
         <v>240</v>
       </c>
       <c r="B1222" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1222">
         <f>1 * 3.6 / 31.58</f>
@@ -27891,7 +27888,7 @@
         <v>242</v>
       </c>
       <c r="B1223" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1223">
         <f>1 * 3.6 / 40.938</f>
@@ -27912,7 +27909,7 @@
         <v>243</v>
       </c>
       <c r="B1224" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1224">
         <f>1 * 3.6 / 50.285</f>
@@ -27933,7 +27930,7 @@
         <v>255</v>
       </c>
       <c r="B1225" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1225">
         <f>1 * 3.6 / 42.5</f>
@@ -27954,7 +27951,7 @@
         <v>262</v>
       </c>
       <c r="B1226" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1226">
         <f>1 / 33.3</f>
@@ -27975,7 +27972,7 @@
         <v>269</v>
       </c>
       <c r="B1227" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1227">
         <f>1 / 33.3</f>
@@ -27996,7 +27993,7 @@
         <v>270</v>
       </c>
       <c r="B1228" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1228">
         <f>1 / 33.3</f>
@@ -28017,7 +28014,7 @@
         <v>271</v>
       </c>
       <c r="B1229" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1229">
         <f>1 / 33.3</f>
@@ -28038,7 +28035,7 @@
         <v>307</v>
       </c>
       <c r="B1230" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1230">
         <f>1 * 3.6 / 43</f>
@@ -28059,7 +28056,7 @@
         <v>326</v>
       </c>
       <c r="B1231" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1231">
         <f>1 * 3.6 / 42.6</f>
@@ -28080,7 +28077,7 @@
         <v>327</v>
       </c>
       <c r="B1232" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1232">
         <f>1 * 3.6 / 39</f>
@@ -28101,7 +28098,7 @@
         <v>332</v>
       </c>
       <c r="B1233" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1233">
         <f>1 / 5.54</f>
@@ -28122,7 +28119,7 @@
         <v>344</v>
       </c>
       <c r="B1234" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1234">
         <f>1 * 3.6 / 39</f>
@@ -28143,7 +28140,7 @@
         <v>351</v>
       </c>
       <c r="B1235" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1235">
         <f>1 * 3.6 / 39</f>
@@ -28164,7 +28161,7 @@
         <v>352</v>
       </c>
       <c r="B1236" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1236">
         <f>1 * 3.6 / 39</f>
@@ -28185,7 +28182,7 @@
         <v>353</v>
       </c>
       <c r="B1237" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1237">
         <f>1 * 3.6 / 46.5</f>
@@ -28206,7 +28203,7 @@
         <v>367</v>
       </c>
       <c r="B1238" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1238">
         <f>1</f>
@@ -28224,7 +28221,7 @@
         <v>374</v>
       </c>
       <c r="B1239" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1239">
         <f>1</f>
@@ -28242,7 +28239,7 @@
         <v>376</v>
       </c>
       <c r="B1240" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1240">
         <f>1 * 3.6 / 32.45</f>
@@ -28263,7 +28260,7 @@
         <v>381</v>
       </c>
       <c r="B1241" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1241">
         <f>1</f>
@@ -28281,7 +28278,7 @@
         <v>382</v>
       </c>
       <c r="B1242" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1242">
         <f>1 * 3.6 / 46.4</f>
@@ -28302,7 +28299,7 @@
         <v>383</v>
       </c>
       <c r="B1243" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1243">
         <f>1 * 3.6 / 45.799</f>
@@ -28323,7 +28320,7 @@
         <v>384</v>
       </c>
       <c r="B1244" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1244">
         <f>1</f>
@@ -28341,7 +28338,7 @@
         <v>385</v>
       </c>
       <c r="B1245" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1245">
         <f>1</f>
@@ -28359,7 +28356,7 @@
         <v>439</v>
       </c>
       <c r="B1246" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1246">
         <f>1</f>
@@ -28377,7 +28374,7 @@
         <v>490</v>
       </c>
       <c r="B1247" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1247">
         <f>1 * 3.6 / 42.43</f>
@@ -28398,7 +28395,7 @@
         <v>561</v>
       </c>
       <c r="B1248" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1248">
         <f>1 * 3.6 / (3900*1000)</f>
@@ -28419,7 +28416,7 @@
         <v>562</v>
       </c>
       <c r="B1249" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1249">
         <f>-1 * 3.6 / 12.35</f>
@@ -28440,7 +28437,7 @@
         <v>563</v>
       </c>
       <c r="B1250" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1250">
         <f>-1 * 3.6 / (6.087*0.95)</f>
@@ -28461,7 +28458,7 @@
         <v>564</v>
       </c>
       <c r="B1251" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1251">
         <f>-1 * 3.6 / 2.453</f>
@@ -28482,7 +28479,7 @@
         <v>565</v>
       </c>
       <c r="B1252" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1252">
         <f>1 * 3.6 / (0.95*15)</f>
@@ -28495,7 +28492,7 @@
         <v>723</v>
       </c>
       <c r="F1252" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="1253" spans="1:6" x14ac:dyDescent="0.35">
@@ -28503,7 +28500,7 @@
         <v>572</v>
       </c>
       <c r="B1253" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1253">
         <f>1 * 3.6 / 15.4</f>
@@ -28524,7 +28521,7 @@
         <v>574</v>
       </c>
       <c r="B1254" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1254">
         <f>1 * 3.6 / 40.961</f>
@@ -28545,7 +28542,7 @@
         <v>716</v>
       </c>
       <c r="B1255" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1255">
         <f>1 * 3.6 / 31.58</f>
@@ -28563,10 +28560,10 @@
     </row>
     <row r="1256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1256" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B1256" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1256">
         <f>1 * 3.6 / 43</f>
@@ -28584,10 +28581,10 @@
     </row>
     <row r="1257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1257" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B1257" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1257">
         <f>1 * 3.6 / 42.6</f>
@@ -28605,10 +28602,10 @@
     </row>
     <row r="1258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1258" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B1258" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1258">
         <f>1 / 5.54</f>
@@ -28629,7 +28626,7 @@
         <v>428</v>
       </c>
       <c r="B1259" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1259">
         <f>1 * 3.6 / 39</f>
@@ -28647,10 +28644,10 @@
     </row>
     <row r="1260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1260" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B1260" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1260">
         <f>1 / (0.777 * 13.1)</f>
@@ -28668,10 +28665,10 @@
     </row>
     <row r="1261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1261" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B1261" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1261">
         <f>1 / (0.777 * 13.1)</f>
@@ -28689,10 +28686,10 @@
     </row>
     <row r="1262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1262" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B1262" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1262">
         <f>1 / (0.777 * 13.1)</f>
@@ -28710,10 +28707,10 @@
     </row>
     <row r="1263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1263" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B1263" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1263">
         <f>1 * 3.6</f>
@@ -28728,10 +28725,10 @@
     </row>
     <row r="1264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1264" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B1264" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1264">
         <f>1 * 3.6</f>
@@ -28746,10 +28743,10 @@
     </row>
     <row r="1265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1265" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B1265" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1265">
         <v>1</v>
@@ -28763,10 +28760,10 @@
     </row>
     <row r="1266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1266" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B1266" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1266">
         <v>1</v>
@@ -28780,10 +28777,10 @@
     </row>
     <row r="1267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1267" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B1267" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1267">
         <v>1</v>
@@ -28797,7 +28794,7 @@
     </row>
     <row r="1268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1268" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B1268" t="s">
         <v>717</v>
@@ -28813,12 +28810,12 @@
         <v>723</v>
       </c>
       <c r="F1268" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="1269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1269" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B1269" t="s">
         <v>717</v>
@@ -28834,12 +28831,12 @@
         <v>723</v>
       </c>
       <c r="F1269" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="1270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1270" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B1270" t="s">
         <v>717</v>
@@ -28855,12 +28852,12 @@
         <v>723</v>
       </c>
       <c r="F1270" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1271" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B1271" t="s">
         <v>717</v>
@@ -28876,12 +28873,12 @@
         <v>723</v>
       </c>
       <c r="F1271" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="1272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1272" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B1272" t="s">
         <v>717</v>
@@ -28897,12 +28894,12 @@
         <v>723</v>
       </c>
       <c r="F1272" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="1273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1273" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B1273" t="s">
         <v>717</v>
@@ -28918,12 +28915,12 @@
         <v>723</v>
       </c>
       <c r="F1273" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="1274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1274" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B1274" t="s">
         <v>717</v>
@@ -28939,12 +28936,12 @@
         <v>723</v>
       </c>
       <c r="F1274" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="1275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1275" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B1275" t="s">
         <v>717</v>
@@ -28960,12 +28957,12 @@
         <v>723</v>
       </c>
       <c r="F1275" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1276" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B1276" t="s">
         <v>717</v>
@@ -28981,12 +28978,12 @@
         <v>723</v>
       </c>
       <c r="F1276" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="1277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1277" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B1277" t="s">
         <v>717</v>
@@ -29002,12 +28999,12 @@
         <v>723</v>
       </c>
       <c r="F1277" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="1278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1278" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B1278" t="s">
         <v>717</v>
@@ -29023,15 +29020,15 @@
         <v>723</v>
       </c>
       <c r="F1278" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="1279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1279" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B1279" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1279">
         <f>3.6/18.43</f>
@@ -29044,15 +29041,15 @@
         <v>723</v>
       </c>
       <c r="F1279" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="1280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1280" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B1280" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1280">
         <f>3.6/18.61</f>
@@ -29065,15 +29062,15 @@
         <v>723</v>
       </c>
       <c r="F1280" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="1281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1281" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B1281" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1281">
         <f>3.6/19.06</f>
@@ -29086,15 +29083,15 @@
         <v>723</v>
       </c>
       <c r="F1281" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1282" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1282" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B1282" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1282">
         <f>3.6/18.93</f>
@@ -29107,15 +29104,15 @@
         <v>723</v>
       </c>
       <c r="F1282" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="1283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1283" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B1283" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1283">
         <f>3.6 / 7.09</f>
@@ -29128,15 +29125,15 @@
         <v>723</v>
       </c>
       <c r="F1283" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="1284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1284" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B1284" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1284">
         <f>3.6/15.34</f>
@@ -29149,15 +29146,15 @@
         <v>723</v>
       </c>
       <c r="F1284" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="1285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1285" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B1285" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1285">
         <f>-1 * 3.6 / 17.09</f>
@@ -29170,15 +29167,15 @@
         <v>723</v>
       </c>
       <c r="F1285" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="1286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1286" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B1286" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1286">
         <f>3.6/15.98</f>
@@ -29191,15 +29188,15 @@
         <v>723</v>
       </c>
       <c r="F1286" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1287" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1287" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B1287" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1287">
         <f>-1 * 3.6 / 11.24</f>
@@ -29212,15 +29209,15 @@
         <v>723</v>
       </c>
       <c r="F1287" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="1288" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1288" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B1288" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1288">
         <f>3.6/18.63</f>
@@ -29233,15 +29230,15 @@
         <v>723</v>
       </c>
       <c r="F1288" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="1289" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1289" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B1289" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1289">
         <f>-1 * 3.6 / 7.64</f>
@@ -29254,12 +29251,12 @@
         <v>723</v>
       </c>
       <c r="F1289" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="1290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1290" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B1290" t="s">
         <v>717</v>
@@ -29275,15 +29272,15 @@
         <v>723</v>
       </c>
       <c r="F1290" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="1291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1291" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B1291" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1291">
         <f>1/10.83</f>
@@ -29296,12 +29293,12 @@
         <v>723</v>
       </c>
       <c r="F1291" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="1292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1292" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B1292" t="s">
         <v>717</v>
@@ -29317,15 +29314,15 @@
         <v>723</v>
       </c>
       <c r="F1292" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="1293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1293" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B1293" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C1293">
         <f>1/10.83</f>
@@ -29338,12 +29335,12 @@
         <v>723</v>
       </c>
       <c r="F1293" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="1294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1294" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B1294" t="s">
         <v>718</v>
@@ -29359,12 +29356,12 @@
         <v>733</v>
       </c>
       <c r="F1294" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1295" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B1295" t="s">
         <v>719</v>
@@ -29381,7 +29378,7 @@
     </row>
     <row r="1296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1296" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B1296" t="s">
         <v>718</v>
@@ -29397,12 +29394,12 @@
         <v>733</v>
       </c>
       <c r="F1296" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1297" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B1297" t="s">
         <v>719</v>
@@ -29419,7 +29416,7 @@
     </row>
     <row r="1298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1298" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B1298" t="s">
         <v>718</v>
@@ -29435,12 +29432,12 @@
         <v>733</v>
       </c>
       <c r="F1298" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1299" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B1299" t="s">
         <v>719</v>
@@ -29457,7 +29454,7 @@
     </row>
     <row r="1300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1300" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B1300" t="s">
         <v>718</v>
@@ -29473,12 +29470,12 @@
         <v>733</v>
       </c>
       <c r="F1300" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1301" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B1301" t="s">
         <v>719</v>
@@ -29495,7 +29492,7 @@
     </row>
     <row r="1302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1302" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B1302" t="s">
         <v>718</v>
@@ -29511,12 +29508,12 @@
         <v>733</v>
       </c>
       <c r="F1302" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1303" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B1303" t="s">
         <v>719</v>
@@ -29533,7 +29530,7 @@
     </row>
     <row r="1304" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1304" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B1304" t="s">
         <v>718</v>
@@ -29549,12 +29546,12 @@
         <v>733</v>
       </c>
       <c r="F1304" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1305" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B1305" t="s">
         <v>719</v>
@@ -29571,7 +29568,7 @@
     </row>
     <row r="1306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1306" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B1306" t="s">
         <v>718</v>
@@ -29587,12 +29584,12 @@
         <v>733</v>
       </c>
       <c r="F1306" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1307" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B1307" t="s">
         <v>719</v>
@@ -29609,7 +29606,7 @@
     </row>
     <row r="1308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1308" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B1308" t="s">
         <v>718</v>
@@ -29625,12 +29622,12 @@
         <v>733</v>
       </c>
       <c r="F1308" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1309" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B1309" t="s">
         <v>719</v>
@@ -29647,7 +29644,7 @@
     </row>
     <row r="1310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1310" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B1310" t="s">
         <v>718</v>
@@ -29663,12 +29660,12 @@
         <v>733</v>
       </c>
       <c r="F1310" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1311" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B1311" t="s">
         <v>719</v>
@@ -29685,7 +29682,7 @@
     </row>
     <row r="1312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1312" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B1312" t="s">
         <v>718</v>
@@ -29701,12 +29698,12 @@
         <v>733</v>
       </c>
       <c r="F1312" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="1313" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1313" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B1313" t="s">
         <v>719</v>
@@ -29723,7 +29720,7 @@
     </row>
     <row r="1314" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1314" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B1314" t="s">
         <v>718</v>
@@ -29739,12 +29736,12 @@
         <v>733</v>
       </c>
       <c r="F1314" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1315" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B1315" t="s">
         <v>719</v>
@@ -29761,7 +29758,7 @@
     </row>
     <row r="1316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1316" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B1316" t="s">
         <v>718</v>
@@ -29777,12 +29774,12 @@
         <v>733</v>
       </c>
       <c r="F1316" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1317" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B1317" t="s">
         <v>719</v>
@@ -29799,7 +29796,7 @@
     </row>
     <row r="1318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1318" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B1318" t="s">
         <v>719</v>
@@ -29816,7 +29813,7 @@
     </row>
     <row r="1319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1319" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B1319" t="s">
         <v>719</v>
@@ -29833,7 +29830,7 @@
     </row>
     <row r="1320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1320" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B1320" t="s">
         <v>719</v>
@@ -29850,7 +29847,7 @@
     </row>
     <row r="1321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1321" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B1321" t="s">
         <v>719</v>
@@ -29867,7 +29864,7 @@
     </row>
     <row r="1322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1322" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B1322" t="s">
         <v>719</v>
